--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:00</t>
+    <t xml:space="preserve">2026-09-09 22:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:52</t>
+    <t xml:space="preserve">2026-09-18 10:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:15</t>
+    <t xml:space="preserve">2026-09-23 12:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:19</t>
+    <t xml:space="preserve">2026-10-02 13:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_s_fonasa_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:50</t>
+    <t xml:space="preserve">2026-10-05 09:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
